--- a/sample.xlsx
+++ b/sample.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,11 +449,6 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
           <t>Date</t>
         </is>
       </c>
@@ -461,7 +456,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MBC</t>
+          <t>ABC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,7 +466,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>info@mbc.ge</t>
+          <t>yusif.axmedov.2008@gmail.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -489,17 +484,16 @@
           <t>SENT</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:37:50</t>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:25:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Crystal</t>
+          <t>Crystally</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,7 +503,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>info@crystal.ge</t>
+          <t>yusifaigemini@gmail.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -522,309 +516,16 @@
           <t>https://crystal.ge</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Rico Express</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Microfinance / Money Transfer</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>info@rico.ge</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://rico.ge</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Lazika Capital</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Microfinance Organization</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>info@lazika.ge</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://lazika.ge</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Credo</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Microfinance Organization</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>info@credo.ge</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://credo.ge</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Swiss Capital</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Microfinance Organization</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>info@swisscapital.ge</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://swisscapital.ge</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Leader Credit</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Microfinance Organization</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>info@leadercredit.ge</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://leadercredit.ge</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Micro Business Capital</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Microfinance Organization</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>info@mbc.ge</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://mbc.ge</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Alliance Group Holding</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Microfinance / Lending</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>info@agh.ge</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://agh.ge</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Smart Finance</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Non-Bank Lender</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>info@smartfinance.ge</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://smartfinance.ge</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Finance Express Georgia</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Non-Bank Lender</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>info@financeexpress.ge</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://financeexpress.ge</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>EuroCredit Georgia</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Non-Bank Lender</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>info@eurocredit.ge</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Tbilisi, Georgia</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://eurocredit.ge</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SENT</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09-03 16:26:47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
